--- a/template_grafico.xlsx
+++ b/template_grafico.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio.rausa\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8B0470-AE74-4887-B984-103CF84567BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +25,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -53,7 +59,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -66,6 +72,2380 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="it-IT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="it-IT"/>
+              <a:t>Confronto Prezzi Carburanti -  [CAD - Avezzano]</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Gasolio</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00FF00"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="roundRect">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFFFF"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="roundRect">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFF00"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="roundRect">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="it-IT"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="13"/>
+              <c:pt idx="0">
+                <c:v>CONAD SELF 24H - Via XX Settembre 411, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>ESSO - XX SETTEMBRE 69 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>ESSO - VIA XX SETTEMBRE 299 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>API-IP - XX SETTEMBRE 328 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>API-IP - VIA PIAZZA TOMMASO DA CELANO SNC 67051, AVEZZANO (AQ) SNC 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>POMPE BIANCHE - VIA P. MATTEOTTI 1 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>POMPE BIANCHE - Via Don Giovanni Minzoni 37 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>POMPE BIANCHE - VIA NUOVA SNC 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>ENI - S.S. 5 Km 113 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>Q8 - S.S. 5 Km 113.060 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>TAMOIL - S.S. 5 TIBURTINA VALERIA KM 117+500 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>POMPE BIANCHE - VIA SANDRO PERTINI snc 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>MEDIA</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="13"/>
+              <c:pt idx="0">
+                <c:v>1.621</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1.659</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1.6579999999999999</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1.649</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>1.665</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>1.6990000000000001</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>1.6990000000000001</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>1.669</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>1.7090000000000001</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>1.6890000000000001</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>1.629</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>1.649</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>1.67</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-C01F-4936-B363-26493C3511CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Benzina</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="70AD47"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00FF00"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="roundRect">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000014-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000015-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000016-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000017-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000">
+                          <a:alpha val="0"/>
+                        </a:sysClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000018-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFFFF"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="roundRect">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000019-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFF00"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="it-IT"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="roundRect">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001A-C01F-4936-B363-26493C3511CA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="it-IT"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="13"/>
+              <c:pt idx="0">
+                <c:v>CONAD SELF 24H - Via XX Settembre 411, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>ESSO - XX SETTEMBRE 69 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>ESSO - VIA XX SETTEMBRE 299 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>API-IP - XX SETTEMBRE 328 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>API-IP - VIA PIAZZA TOMMASO DA CELANO SNC 67051, AVEZZANO (AQ) SNC 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>POMPE BIANCHE - VIA P. MATTEOTTI 1 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>POMPE BIANCHE - Via Don Giovanni Minzoni 37 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>POMPE BIANCHE - VIA NUOVA SNC 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>ENI - S.S. 5 Km 113 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>Q8 - S.S. 5 Km 113.060 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>TAMOIL - S.S. 5 TIBURTINA VALERIA KM 117+500 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>POMPE BIANCHE - VIA SANDRO PERTINI snc 67051, Avezzano</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>MEDIA</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="13"/>
+              <c:pt idx="0">
+                <c:v>1.569</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1.6279999999999999</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1.633</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1.619</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>1.645</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>1.679</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>1.679</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>1.609</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>1.649</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>1.649</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>1.6080000000000001</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>1.6990000000000001</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>1.645</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001B-C01F-4936-B363-26493C3511CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="1147168719"/>
+        <c:axId val="1147152399"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1147168719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1147152399"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1147152399"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1147168719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="it-IT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Grafico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48A618F4-0B57-42D3-A04E-6A492518749B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +2710,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>